--- a/待租单元.xlsx
+++ b/待租单元.xlsx
@@ -1112,7 +1112,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="13" customWidth="1" style="6" min="2" max="2"/>
@@ -1172,7 +1172,7 @@
     </row>
     <row r="3" ht="16.5" customHeight="1" s="6">
       <c r="A3" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B3" s="3" t="n">
         <v>510</v>
@@ -1198,7 +1198,7 @@
     </row>
     <row r="4" ht="16.5" customHeight="1" s="6">
       <c r="A4" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B4" s="3" t="n">
         <v>602</v>
@@ -1224,7 +1224,7 @@
     </row>
     <row r="5" ht="16.5" customHeight="1" s="6">
       <c r="A5" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B5" s="3" t="n">
         <v>615</v>
@@ -1250,7 +1250,7 @@
     </row>
     <row r="6" ht="16.5" customHeight="1" s="6">
       <c r="A6" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B6" s="3" t="n">
         <v>806</v>
@@ -1276,7 +1276,7 @@
     </row>
     <row r="7" ht="16.5" customHeight="1" s="6">
       <c r="A7" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
     </row>
     <row r="8" ht="16.5" customHeight="1" s="6">
       <c r="A8" s="3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B8" s="3" t="n">
         <v>1003</v>
@@ -1330,7 +1330,7 @@
     </row>
     <row r="9" ht="16.5" customHeight="1" s="6">
       <c r="A9" s="3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B9" s="3" t="n">
         <v>1006</v>
@@ -1356,7 +1356,7 @@
     </row>
     <row r="10" ht="16.5" customHeight="1" s="6">
       <c r="A10" s="3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B10" s="3" t="n">
         <v>1010</v>
@@ -1382,7 +1382,7 @@
     </row>
     <row r="11" ht="16.5" customHeight="1" s="6">
       <c r="A11" s="3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B11" s="3" t="n">
         <v>1207</v>
@@ -1408,22 +1408,24 @@
     </row>
     <row r="12" ht="16.5" customHeight="1" s="6">
       <c r="A12" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="B12" s="3" t="n">
-        <v>1213</v>
+        <v>10</v>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>13A02</t>
+        </is>
       </c>
       <c r="C12" s="9" t="n">
-        <v>167</v>
+        <v>177</v>
       </c>
       <c r="D12" s="10" t="n">
         <v>56</v>
       </c>
       <c r="E12" s="10" t="n">
-        <v>9000</v>
+        <v>9500</v>
       </c>
       <c r="F12" s="10">
-        <f>E14/C14</f>
+        <f>E15/C15</f>
         <v/>
       </c>
       <c r="G12" s="3" t="inlineStr">
@@ -1434,15 +1436,15 @@
     </row>
     <row r="13" ht="16.5" customHeight="1" s="6">
       <c r="A13" s="3" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>13A02</t>
+          <t>13A15</t>
         </is>
       </c>
       <c r="C13" s="9" t="n">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D13" s="10" t="n">
         <v>56</v>
@@ -1451,7 +1453,7 @@
         <v>9500</v>
       </c>
       <c r="F13" s="10">
-        <f>E15/C15</f>
+        <f>E16/C16</f>
         <v/>
       </c>
       <c r="G13" s="3" t="inlineStr">
@@ -1462,80 +1464,78 @@
     </row>
     <row r="14" ht="16.5" customHeight="1" s="6">
       <c r="A14" s="3" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>13A15</t>
+          <t>1605+1606</t>
         </is>
       </c>
       <c r="C14" s="9" t="n">
-        <v>178</v>
+        <v>386</v>
       </c>
       <c r="D14" s="10" t="n">
         <v>56</v>
       </c>
       <c r="E14" s="10" t="n">
-        <v>9500</v>
+        <v>20800</v>
       </c>
       <c r="F14" s="10">
-        <f>E16/C16</f>
+        <f>E17/C17</f>
         <v/>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>双边采光 2+1</t>
+          <t>带装修 4+1</t>
         </is>
       </c>
     </row>
     <row r="15" ht="16.5" customHeight="1" s="6">
       <c r="A15" s="3" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>1605+1606</t>
+          <t>1609-2</t>
         </is>
       </c>
       <c r="C15" s="9" t="n">
-        <v>386</v>
+        <v>168</v>
       </c>
       <c r="D15" s="10" t="n">
         <v>56</v>
       </c>
       <c r="E15" s="10" t="n">
-        <v>20800</v>
+        <v>9000</v>
       </c>
       <c r="F15" s="10">
-        <f>E17/C17</f>
+        <f>E18/C18</f>
         <v/>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>带装修 4+1</t>
+          <t>双边采光</t>
         </is>
       </c>
     </row>
     <row r="16" ht="16.5" customHeight="1" s="6">
       <c r="A16" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>1609-2</t>
-        </is>
+        <v>14</v>
+      </c>
+      <c r="B16" s="3" t="n">
+        <v>1702</v>
       </c>
       <c r="C16" s="9" t="n">
-        <v>168</v>
+        <v>263</v>
       </c>
       <c r="D16" s="10" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E16" s="10" t="n">
-        <v>9000</v>
+        <v>13800</v>
       </c>
       <c r="F16" s="10">
-        <f>E18/C18</f>
+        <f>E19/C19</f>
         <v/>
       </c>
       <c r="G16" s="3" t="inlineStr">
@@ -1546,100 +1546,100 @@
     </row>
     <row r="17" ht="16.5" customHeight="1" s="6">
       <c r="A17" s="3" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B17" s="3" t="n">
-        <v>1702</v>
+        <v>1802</v>
       </c>
       <c r="C17" s="9" t="n">
-        <v>263</v>
+        <v>177</v>
       </c>
       <c r="D17" s="10" t="n">
         <v>57</v>
       </c>
       <c r="E17" s="10" t="n">
-        <v>13800</v>
+        <v>9600</v>
       </c>
       <c r="F17" s="10">
-        <f>E19/C19</f>
+        <f>E20/C20</f>
         <v/>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>双边采光</t>
+          <t>双边采光 2+1</t>
         </is>
       </c>
     </row>
     <row r="18" ht="16.5" customHeight="1" s="6">
       <c r="A18" s="3" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B18" s="3" t="n">
-        <v>1802</v>
+        <v>1809</v>
       </c>
       <c r="C18" s="9" t="n">
-        <v>177</v>
+        <v>201</v>
       </c>
       <c r="D18" s="10" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E18" s="10" t="n">
-        <v>9600</v>
+        <v>11000</v>
       </c>
       <c r="F18" s="10">
-        <f>E20/C20</f>
+        <f>E21/C21</f>
         <v/>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>双边采光 2+1</t>
+          <t>方正好用大通间</t>
         </is>
       </c>
     </row>
     <row r="19" ht="16.5" customHeight="1" s="6">
       <c r="A19" s="3" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B19" s="3" t="n">
-        <v>1809</v>
+        <v>1810</v>
       </c>
       <c r="C19" s="9" t="n">
         <v>201</v>
       </c>
       <c r="D19" s="10" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E19" s="10" t="n">
         <v>11000</v>
       </c>
       <c r="F19" s="10">
-        <f>E21/C21</f>
+        <f>E22/C22</f>
         <v/>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>方正好用大通间</t>
+          <t>双边采光 2+1</t>
         </is>
       </c>
     </row>
     <row r="20" ht="16.5" customHeight="1" s="6">
       <c r="A20" s="3" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B20" s="3" t="n">
-        <v>1810</v>
+        <v>1815</v>
       </c>
       <c r="C20" s="9" t="n">
-        <v>201</v>
+        <v>178</v>
       </c>
       <c r="D20" s="10" t="n">
         <v>57</v>
       </c>
       <c r="E20" s="10" t="n">
-        <v>11000</v>
+        <v>9600</v>
       </c>
       <c r="F20" s="10">
-        <f>E22/C22</f>
+        <f>E23/C23</f>
         <v/>
       </c>
       <c r="G20" s="3" t="inlineStr">
@@ -1650,100 +1650,100 @@
     </row>
     <row r="21" ht="16.5" customHeight="1" s="6">
       <c r="A21" s="3" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B21" s="3" t="n">
-        <v>1815</v>
+        <v>1907</v>
       </c>
       <c r="C21" s="9" t="n">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D21" s="10" t="n">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="E21" s="10" t="n">
-        <v>9600</v>
+        <v>10500</v>
       </c>
       <c r="F21" s="10">
-        <f>E23/C23</f>
+        <f>E26/C26</f>
         <v/>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>双边采光 2+1</t>
+          <t>双边采光赠阳台</t>
         </is>
       </c>
     </row>
     <row r="22" ht="16.5" customHeight="1" s="6">
       <c r="A22" s="3" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B22" s="3" t="n">
-        <v>1907</v>
+        <v>1916</v>
       </c>
       <c r="C22" s="9" t="n">
-        <v>179</v>
+        <v>218</v>
       </c>
       <c r="D22" s="10" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E22" s="10" t="n">
-        <v>10500</v>
+        <v>12500</v>
       </c>
       <c r="F22" s="10">
-        <f>E26/C26</f>
+        <f>E27/C27</f>
         <v/>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>双边采光赠阳台</t>
+          <t>方正好用大通间</t>
         </is>
       </c>
     </row>
     <row r="23" ht="16.5" customHeight="1" s="6">
       <c r="A23" s="3" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B23" s="3" t="n">
-        <v>1916</v>
+        <v>2002</v>
       </c>
       <c r="C23" s="9" t="n">
-        <v>218</v>
+        <v>157</v>
       </c>
       <c r="D23" s="10" t="n">
         <v>60</v>
       </c>
       <c r="E23" s="10" t="n">
-        <v>12500</v>
+        <v>9000</v>
       </c>
       <c r="F23" s="10">
-        <f>E27/C27</f>
+        <f>E28/C28</f>
         <v/>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>方正好用大通间</t>
+          <t>双边采光</t>
         </is>
       </c>
     </row>
     <row r="24" ht="16.5" customHeight="1" s="6">
       <c r="A24" s="3" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B24" s="3" t="n">
-        <v>2002</v>
+        <v>2007</v>
       </c>
       <c r="C24" s="9" t="n">
-        <v>157</v>
+        <v>185</v>
       </c>
       <c r="D24" s="10" t="n">
         <v>60</v>
       </c>
       <c r="E24" s="10" t="n">
-        <v>9000</v>
+        <v>10500</v>
       </c>
       <c r="F24" s="10">
-        <f>E28/C28</f>
+        <f>E29/C29</f>
         <v/>
       </c>
       <c r="G24" s="3" t="inlineStr">
@@ -1754,48 +1754,48 @@
     </row>
     <row r="25" ht="16.5" customHeight="1" s="6">
       <c r="A25" s="3" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B25" s="3" t="n">
-        <v>2007</v>
+        <v>2008</v>
       </c>
       <c r="C25" s="9" t="n">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D25" s="10" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E25" s="10" t="n">
-        <v>10500</v>
+        <v>10800</v>
       </c>
       <c r="F25" s="10">
-        <f>E29/C29</f>
+        <f>E30/C30</f>
         <v/>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>双边采光</t>
+          <t>方正好用大通间</t>
         </is>
       </c>
     </row>
     <row r="26" ht="16.5" customHeight="1" s="6">
       <c r="A26" s="3" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B26" s="3" t="n">
-        <v>2008</v>
+        <v>2009</v>
       </c>
       <c r="C26" s="9" t="n">
-        <v>186</v>
+        <v>201</v>
       </c>
       <c r="D26" s="10" t="n">
         <v>62</v>
       </c>
       <c r="E26" s="10" t="n">
-        <v>10800</v>
+        <v>11800</v>
       </c>
       <c r="F26" s="10">
-        <f>E30/C30</f>
+        <f>E31/C31</f>
         <v/>
       </c>
       <c r="G26" s="3" t="inlineStr">
@@ -1806,108 +1806,33 @@
     </row>
     <row r="27" ht="16.5" customHeight="1" s="6">
       <c r="A27" s="3" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B27" s="3" t="n">
-        <v>2009</v>
+        <v>2015</v>
       </c>
       <c r="C27" s="9" t="n">
-        <v>201</v>
+        <v>160</v>
       </c>
       <c r="D27" s="10" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E27" s="10" t="n">
-        <v>11800</v>
+        <v>9200</v>
       </c>
       <c r="F27" s="10">
-        <f>E31/C31</f>
+        <f>E34/C34</f>
         <v/>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>方正好用大通间</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="16.5" customHeight="1" s="6">
-      <c r="A28" s="3" t="n">
-        <v>30</v>
-      </c>
-      <c r="B28" s="3" t="n">
-        <v>2012</v>
-      </c>
-      <c r="C28" s="9" t="n">
-        <v>121</v>
-      </c>
-      <c r="D28" s="10" t="n">
-        <v>63</v>
-      </c>
-      <c r="E28" s="10" t="n">
-        <v>7300</v>
-      </c>
-      <c r="F28" s="10">
-        <f>E32/C32</f>
-        <v/>
-      </c>
-      <c r="G28" s="3" t="inlineStr">
-        <is>
-          <t>高层北向小面积</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="16.5" customHeight="1" s="6">
-      <c r="A29" s="3" t="n">
-        <v>31</v>
-      </c>
-      <c r="B29" s="3" t="n">
-        <v>2013</v>
-      </c>
-      <c r="C29" s="9" t="n">
-        <v>120</v>
-      </c>
-      <c r="D29" s="10" t="n">
-        <v>63</v>
-      </c>
-      <c r="E29" s="10" t="n">
-        <v>7300</v>
-      </c>
-      <c r="F29" s="10">
-        <f>E33/C33</f>
-        <v/>
-      </c>
-      <c r="G29" s="3" t="inlineStr">
-        <is>
-          <t>高层北向小面积</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="16.5" customHeight="1" s="6">
-      <c r="A30" s="3" t="n">
-        <v>32</v>
-      </c>
-      <c r="B30" s="3" t="n">
-        <v>2015</v>
-      </c>
-      <c r="C30" s="9" t="n">
-        <v>160</v>
-      </c>
-      <c r="D30" s="10" t="n">
-        <v>60</v>
-      </c>
-      <c r="E30" s="10" t="n">
-        <v>9200</v>
-      </c>
-      <c r="F30" s="10">
-        <f>E34/C34</f>
-        <v/>
-      </c>
-      <c r="G30" s="3" t="inlineStr">
-        <is>
           <t>双边采光</t>
         </is>
       </c>
     </row>
+    <row r="28" ht="16.5" customHeight="1" s="6"/>
+    <row r="29" ht="16.5" customHeight="1" s="6"/>
+    <row r="30" ht="16.5" customHeight="1" s="6"/>
     <row r="31" ht="16.5" customHeight="1" s="6"/>
     <row r="32" ht="16.5" customHeight="1" s="6"/>
     <row r="33" ht="16.5" customHeight="1" s="6"/>

--- a/待租单元.xlsx
+++ b/待租单元.xlsx
@@ -1112,7 +1112,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="13" customWidth="1" style="6" min="2" max="2"/>
@@ -1330,74 +1330,76 @@
     </row>
     <row r="9" ht="16.5" customHeight="1" s="6">
       <c r="A9" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B9" s="3" t="n">
-        <v>1006</v>
+        <v>1010</v>
       </c>
       <c r="C9" s="9" t="n">
-        <v>246</v>
+        <v>228</v>
       </c>
       <c r="D9" s="10" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="E9" s="10" t="n">
-        <v>13500</v>
+        <v>12200</v>
       </c>
       <c r="F9" s="10">
-        <f>E10/C10</f>
+        <f>E11/C11</f>
         <v/>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>方正户型 1+1</t>
+          <t>双边采光 1+1</t>
         </is>
       </c>
     </row>
     <row r="10" ht="16.5" customHeight="1" s="6">
       <c r="A10" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B10" s="3" t="n">
-        <v>1010</v>
+        <v>1207</v>
       </c>
       <c r="C10" s="9" t="n">
-        <v>228</v>
+        <v>192</v>
       </c>
       <c r="D10" s="10" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E10" s="10" t="n">
-        <v>12200</v>
+        <v>10200</v>
       </c>
       <c r="F10" s="10">
-        <f>E11/C11</f>
+        <f>E12/C12</f>
         <v/>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>双边采光 1+1</t>
+          <t>双边采光 2+1</t>
         </is>
       </c>
     </row>
     <row r="11" ht="16.5" customHeight="1" s="6">
       <c r="A11" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="B11" s="3" t="n">
-        <v>1207</v>
+        <v>10</v>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>13A02</t>
+        </is>
       </c>
       <c r="C11" s="9" t="n">
-        <v>192</v>
+        <v>177</v>
       </c>
       <c r="D11" s="10" t="n">
         <v>56</v>
       </c>
       <c r="E11" s="10" t="n">
-        <v>10200</v>
+        <v>9500</v>
       </c>
       <c r="F11" s="10">
-        <f>E12/C12</f>
+        <f>E15/C15</f>
         <v/>
       </c>
       <c r="G11" s="3" t="inlineStr">
@@ -1408,15 +1410,15 @@
     </row>
     <row r="12" ht="16.5" customHeight="1" s="6">
       <c r="A12" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>13A02</t>
+          <t>13A15</t>
         </is>
       </c>
       <c r="C12" s="9" t="n">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D12" s="10" t="n">
         <v>56</v>
@@ -1425,7 +1427,7 @@
         <v>9500</v>
       </c>
       <c r="F12" s="10">
-        <f>E15/C15</f>
+        <f>E16/C16</f>
         <v/>
       </c>
       <c r="G12" s="3" t="inlineStr">
@@ -1436,80 +1438,78 @@
     </row>
     <row r="13" ht="16.5" customHeight="1" s="6">
       <c r="A13" s="3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>13A15</t>
+          <t>1605+1606</t>
         </is>
       </c>
       <c r="C13" s="9" t="n">
-        <v>178</v>
+        <v>386</v>
       </c>
       <c r="D13" s="10" t="n">
         <v>56</v>
       </c>
       <c r="E13" s="10" t="n">
-        <v>9500</v>
+        <v>20800</v>
       </c>
       <c r="F13" s="10">
-        <f>E16/C16</f>
+        <f>E17/C17</f>
         <v/>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>双边采光 2+1</t>
+          <t>带装修 4+1</t>
         </is>
       </c>
     </row>
     <row r="14" ht="16.5" customHeight="1" s="6">
       <c r="A14" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>1605+1606</t>
+          <t>1609-2</t>
         </is>
       </c>
       <c r="C14" s="9" t="n">
-        <v>386</v>
+        <v>168</v>
       </c>
       <c r="D14" s="10" t="n">
         <v>56</v>
       </c>
       <c r="E14" s="10" t="n">
-        <v>20800</v>
+        <v>9000</v>
       </c>
       <c r="F14" s="10">
-        <f>E17/C17</f>
+        <f>E18/C18</f>
         <v/>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>带装修 4+1</t>
+          <t>双边采光</t>
         </is>
       </c>
     </row>
     <row r="15" ht="16.5" customHeight="1" s="6">
       <c r="A15" s="3" t="n">
-        <v>13</v>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>1609-2</t>
-        </is>
+        <v>14</v>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>1702</v>
       </c>
       <c r="C15" s="9" t="n">
-        <v>168</v>
+        <v>263</v>
       </c>
       <c r="D15" s="10" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E15" s="10" t="n">
-        <v>9000</v>
+        <v>13800</v>
       </c>
       <c r="F15" s="10">
-        <f>E18/C18</f>
+        <f>E19/C19</f>
         <v/>
       </c>
       <c r="G15" s="3" t="inlineStr">
@@ -1520,48 +1520,48 @@
     </row>
     <row r="16" ht="16.5" customHeight="1" s="6">
       <c r="A16" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B16" s="3" t="n">
-        <v>1702</v>
+        <v>1802</v>
       </c>
       <c r="C16" s="9" t="n">
-        <v>263</v>
+        <v>177</v>
       </c>
       <c r="D16" s="10" t="n">
         <v>57</v>
       </c>
       <c r="E16" s="10" t="n">
-        <v>13800</v>
+        <v>9600</v>
       </c>
       <c r="F16" s="10">
-        <f>E19/C19</f>
+        <f>E20/C20</f>
         <v/>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>双边采光</t>
+          <t>双边采光 2+1</t>
         </is>
       </c>
     </row>
     <row r="17" ht="16.5" customHeight="1" s="6">
       <c r="A17" s="3" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B17" s="3" t="n">
-        <v>1802</v>
+        <v>1810</v>
       </c>
       <c r="C17" s="9" t="n">
-        <v>177</v>
+        <v>201</v>
       </c>
       <c r="D17" s="10" t="n">
         <v>57</v>
       </c>
       <c r="E17" s="10" t="n">
-        <v>9600</v>
+        <v>11000</v>
       </c>
       <c r="F17" s="10">
-        <f>E20/C20</f>
+        <f>E22/C22</f>
         <v/>
       </c>
       <c r="G17" s="3" t="inlineStr">
@@ -1572,264 +1572,139 @@
     </row>
     <row r="18" ht="16.5" customHeight="1" s="6">
       <c r="A18" s="3" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B18" s="3" t="n">
-        <v>1809</v>
+        <v>1815</v>
       </c>
       <c r="C18" s="9" t="n">
-        <v>201</v>
+        <v>178</v>
       </c>
       <c r="D18" s="10" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E18" s="10" t="n">
-        <v>11000</v>
+        <v>9600</v>
       </c>
       <c r="F18" s="10">
-        <f>E21/C21</f>
+        <f>E23/C23</f>
         <v/>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>方正好用大通间</t>
+          <t>双边采光 2+1</t>
         </is>
       </c>
     </row>
     <row r="19" ht="16.5" customHeight="1" s="6">
       <c r="A19" s="3" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B19" s="3" t="n">
-        <v>1810</v>
+        <v>1907</v>
       </c>
       <c r="C19" s="9" t="n">
-        <v>201</v>
+        <v>179</v>
       </c>
       <c r="D19" s="10" t="n">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="E19" s="10" t="n">
-        <v>11000</v>
+        <v>10500</v>
       </c>
       <c r="F19" s="10">
-        <f>E22/C22</f>
+        <f>E26/C26</f>
         <v/>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>双边采光 2+1</t>
+          <t>双边采光赠阳台</t>
         </is>
       </c>
     </row>
     <row r="20" ht="16.5" customHeight="1" s="6">
       <c r="A20" s="3" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B20" s="3" t="n">
-        <v>1815</v>
+        <v>2002</v>
       </c>
       <c r="C20" s="9" t="n">
-        <v>178</v>
+        <v>157</v>
       </c>
       <c r="D20" s="10" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E20" s="10" t="n">
-        <v>9600</v>
+        <v>9000</v>
       </c>
       <c r="F20" s="10">
-        <f>E23/C23</f>
+        <f>E28/C28</f>
         <v/>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>双边采光 2+1</t>
+          <t>双边采光</t>
         </is>
       </c>
     </row>
     <row r="21" ht="16.5" customHeight="1" s="6">
       <c r="A21" s="3" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B21" s="3" t="n">
-        <v>1907</v>
+        <v>2007</v>
       </c>
       <c r="C21" s="9" t="n">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="D21" s="10" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E21" s="10" t="n">
         <v>10500</v>
       </c>
       <c r="F21" s="10">
-        <f>E26/C26</f>
+        <f>E29/C29</f>
         <v/>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>双边采光赠阳台</t>
+          <t>双边采光</t>
         </is>
       </c>
     </row>
     <row r="22" ht="16.5" customHeight="1" s="6">
       <c r="A22" s="3" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="B22" s="3" t="n">
-        <v>1916</v>
+        <v>2015</v>
       </c>
       <c r="C22" s="9" t="n">
-        <v>218</v>
+        <v>160</v>
       </c>
       <c r="D22" s="10" t="n">
         <v>60</v>
       </c>
       <c r="E22" s="10" t="n">
-        <v>12500</v>
+        <v>9200</v>
       </c>
       <c r="F22" s="10">
-        <f>E27/C27</f>
+        <f>E34/C34</f>
         <v/>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>方正好用大通间</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="16.5" customHeight="1" s="6">
-      <c r="A23" s="3" t="n">
-        <v>21</v>
-      </c>
-      <c r="B23" s="3" t="n">
-        <v>2002</v>
-      </c>
-      <c r="C23" s="9" t="n">
-        <v>157</v>
-      </c>
-      <c r="D23" s="10" t="n">
-        <v>60</v>
-      </c>
-      <c r="E23" s="10" t="n">
-        <v>9000</v>
-      </c>
-      <c r="F23" s="10">
-        <f>E28/C28</f>
-        <v/>
-      </c>
-      <c r="G23" s="3" t="inlineStr">
-        <is>
           <t>双边采光</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="16.5" customHeight="1" s="6">
-      <c r="A24" s="3" t="n">
-        <v>22</v>
-      </c>
-      <c r="B24" s="3" t="n">
-        <v>2007</v>
-      </c>
-      <c r="C24" s="9" t="n">
-        <v>185</v>
-      </c>
-      <c r="D24" s="10" t="n">
-        <v>60</v>
-      </c>
-      <c r="E24" s="10" t="n">
-        <v>10500</v>
-      </c>
-      <c r="F24" s="10">
-        <f>E29/C29</f>
-        <v/>
-      </c>
-      <c r="G24" s="3" t="inlineStr">
-        <is>
-          <t>双边采光</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="16.5" customHeight="1" s="6">
-      <c r="A25" s="3" t="n">
-        <v>23</v>
-      </c>
-      <c r="B25" s="3" t="n">
-        <v>2008</v>
-      </c>
-      <c r="C25" s="9" t="n">
-        <v>186</v>
-      </c>
-      <c r="D25" s="10" t="n">
-        <v>62</v>
-      </c>
-      <c r="E25" s="10" t="n">
-        <v>10800</v>
-      </c>
-      <c r="F25" s="10">
-        <f>E30/C30</f>
-        <v/>
-      </c>
-      <c r="G25" s="3" t="inlineStr">
-        <is>
-          <t>方正好用大通间</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="16.5" customHeight="1" s="6">
-      <c r="A26" s="3" t="n">
-        <v>24</v>
-      </c>
-      <c r="B26" s="3" t="n">
-        <v>2009</v>
-      </c>
-      <c r="C26" s="9" t="n">
-        <v>201</v>
-      </c>
-      <c r="D26" s="10" t="n">
-        <v>62</v>
-      </c>
-      <c r="E26" s="10" t="n">
-        <v>11800</v>
-      </c>
-      <c r="F26" s="10">
-        <f>E31/C31</f>
-        <v/>
-      </c>
-      <c r="G26" s="3" t="inlineStr">
-        <is>
-          <t>方正好用大通间</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="16.5" customHeight="1" s="6">
-      <c r="A27" s="3" t="n">
-        <v>25</v>
-      </c>
-      <c r="B27" s="3" t="n">
-        <v>2015</v>
-      </c>
-      <c r="C27" s="9" t="n">
-        <v>160</v>
-      </c>
-      <c r="D27" s="10" t="n">
-        <v>60</v>
-      </c>
-      <c r="E27" s="10" t="n">
-        <v>9200</v>
-      </c>
-      <c r="F27" s="10">
-        <f>E34/C34</f>
-        <v/>
-      </c>
-      <c r="G27" s="3" t="inlineStr">
-        <is>
-          <t>双边采光</t>
-        </is>
-      </c>
-    </row>
+    <row r="23" ht="16.5" customHeight="1" s="6"/>
+    <row r="24" ht="16.5" customHeight="1" s="6"/>
+    <row r="25" ht="16.5" customHeight="1" s="6"/>
+    <row r="26" ht="16.5" customHeight="1" s="6"/>
+    <row r="27" ht="16.5" customHeight="1" s="6"/>
     <row r="28" ht="16.5" customHeight="1" s="6"/>
     <row r="29" ht="16.5" customHeight="1" s="6"/>
     <row r="30" ht="16.5" customHeight="1" s="6"/>
